--- a/01_Input/00_CO Validation/South Sudan - Energy Projects.xlsx
+++ b/01_Input/00_CO Validation/South Sudan - Energy Projects.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="27226"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="28429"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://undp.sharepoint.com/sites/UNDPSustainableEnergyHub/Shared Documents/General/0. CURRENT FOLDER - Sustainable Energy Hub/05. Accounting for Progress to 500M/7. CO Validation/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1266" documentId="8_{8CAB50D8-CF81-BC4A-BCD6-641596546354}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{AE811436-E7E0-4CBD-BE3C-4C6884C29CB8}"/>
+  <xr:revisionPtr revIDLastSave="1285" documentId="8_{8CAB50D8-CF81-BC4A-BCD6-641596546354}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CAABFB39-D486-40AF-8738-7D04AEFFF3DE}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Projects (3)" sheetId="4" r:id="rId1"/>
-    <sheet name="Projects (2)" sheetId="3" r:id="rId2"/>
-    <sheet name="Projects" sheetId="1" r:id="rId3"/>
+    <sheet name="Projects (2)" sheetId="3" state="hidden" r:id="rId2"/>
+    <sheet name="Projects" sheetId="1" state="hidden" r:id="rId3"/>
     <sheet name="Beneficiary Categories" sheetId="2" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191028"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="328" uniqueCount="115">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="296" uniqueCount="115">
   <si>
     <t>Project ID</t>
   </si>
@@ -131,9 +131,6 @@
     <t>Unknown</t>
   </si>
   <si>
-    <t>j</t>
-  </si>
-  <si>
     <t>00080877, 00097821, 00080982, 00109097</t>
   </si>
   <si>
@@ -150,9 +147,6 @@
   </si>
   <si>
     <t>Close the gap on energy access</t>
-  </si>
-  <si>
-    <t>Renewable Energy</t>
   </si>
   <si>
     <t>93664</t>
@@ -195,55 +189,61 @@
     <t>Agriculture and Food System</t>
   </si>
   <si>
+    <t>125900</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Global Fund Project - Solar for Health</t>
+  </si>
+  <si>
+    <t>Health Services</t>
+  </si>
+  <si>
+    <t>On Going, 9000000 was marked by CO. 28 hospitals and health facilities across the country. Of these, new solar Photovoltaic (PV) systems are being installed in 19 health facilities; while for nine health facilities, battery replacements are being planned because they have already existing solar PV systems. Assuming 100000 per hosptial and 20000 per facility.</t>
+  </si>
+  <si>
+    <t>Solar4Health</t>
+  </si>
+  <si>
+    <t>Category</t>
+  </si>
+  <si>
+    <t>Comments</t>
+  </si>
+  <si>
+    <t>00115727</t>
+  </si>
+  <si>
+    <t>124, 570.12</t>
+  </si>
+  <si>
+    <t>Renewable Energy</t>
+  </si>
+  <si>
+    <t>00093664</t>
+  </si>
+  <si>
+    <t>00104022</t>
+  </si>
+  <si>
+    <t>00101178</t>
+  </si>
+  <si>
+    <t>Agricultural Services</t>
+  </si>
+  <si>
     <t>Energy Efficiency</t>
   </si>
   <si>
-    <t>125900</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Global Fund Project - Solar for Health</t>
-  </si>
-  <si>
-    <t>Health Services</t>
+    <t>00125900</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Global Fund Project - Solar for Heath </t>
   </si>
   <si>
     <t>On Going</t>
   </si>
   <si>
-    <t>Solar4Health</t>
-  </si>
-  <si>
     <t>Large number.</t>
-  </si>
-  <si>
-    <t>Category</t>
-  </si>
-  <si>
-    <t>Comments</t>
-  </si>
-  <si>
-    <t>00115727</t>
-  </si>
-  <si>
-    <t>124, 570.12</t>
-  </si>
-  <si>
-    <t>00093664</t>
-  </si>
-  <si>
-    <t>00104022</t>
-  </si>
-  <si>
-    <t>00101178</t>
-  </si>
-  <si>
-    <t>Agricultural Services</t>
-  </si>
-  <si>
-    <t>00125900</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Global Fund Project - Solar for Heath </t>
   </si>
   <si>
     <t xml:space="preserve">Comments </t>
@@ -401,10 +401,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
-    <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="165" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
   </numFmts>
-  <fonts count="18">
+  <fonts count="18" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -525,7 +526,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -541,6 +542,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.79998168889431442"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -626,7 +633,7 @@
       <protection locked="0"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="73">
+  <cellXfs count="80">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -679,7 +686,7 @@
     <xf numFmtId="49" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -700,13 +707,13 @@
     <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -741,15 +748,6 @@
     <xf numFmtId="49" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="43" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
@@ -762,44 +760,11 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="4" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="4" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="49" fontId="5" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="43" fontId="5" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -828,6 +793,69 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="4" fontId="7" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="4" fontId="5" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="7" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="5" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="5" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -1146,19 +1174,19 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:AD11"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15.75"/>
+  <dimension ref="A1:V11"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="46.5703125" style="23" customWidth="1"/>
     <col min="2" max="2" width="54.140625" style="23" customWidth="1"/>
     <col min="3" max="3" width="12" style="23" customWidth="1"/>
-    <col min="4" max="4" width="14.28515625" style="27" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="21" style="28" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="46.85546875" style="29" customWidth="1"/>
-    <col min="7" max="7" width="9.140625" style="28" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="12.85546875" style="30" customWidth="1"/>
-    <col min="9" max="9" width="19.28515625" style="29" customWidth="1"/>
-    <col min="10" max="10" width="13" style="28" customWidth="1"/>
+    <col min="4" max="4" width="15" style="69" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="21" style="70" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="46.85546875" style="71" customWidth="1"/>
+    <col min="7" max="7" width="9.140625" style="70" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="12.85546875" style="76" customWidth="1"/>
+    <col min="9" max="9" width="35.85546875" style="71" customWidth="1"/>
+    <col min="10" max="10" width="13" style="70" customWidth="1"/>
     <col min="11" max="11" width="12.42578125" style="23" customWidth="1"/>
     <col min="12" max="12" width="12.85546875" style="23" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="16.140625" style="23" customWidth="1"/>
@@ -1171,7 +1199,7 @@
     <col min="21" max="16384" width="8.85546875" style="23"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:30" ht="32.25">
+    <row r="1" spans="1:22" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A1" s="16" t="s">
         <v>0</v>
       </c>
@@ -1181,63 +1209,63 @@
       <c r="C1" s="16" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="16" t="s">
+      <c r="D1" s="56" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="16" t="s">
+      <c r="E1" s="56" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="16" t="s">
+      <c r="F1" s="56" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="16" t="s">
+      <c r="G1" s="56" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="16" t="s">
+      <c r="H1" s="73" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="16" t="s">
+      <c r="I1" s="56" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="16" t="s">
+      <c r="J1" s="56" t="s">
         <v>9</v>
       </c>
       <c r="K1" s="16" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="63" t="s">
+      <c r="L1" s="49" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="64" t="s">
+      <c r="M1" s="50" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="63" t="s">
+      <c r="N1" s="49" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="63" t="s">
+      <c r="O1" s="49" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="64" t="s">
+      <c r="P1" s="50" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" s="64" t="s">
+      <c r="Q1" s="50" t="s">
         <v>16</v>
       </c>
-      <c r="R1" s="65" t="s">
+      <c r="R1" s="51" t="s">
         <v>17</v>
       </c>
-      <c r="S1" s="66" t="s">
+      <c r="S1" s="52" t="s">
         <v>18</v>
       </c>
-      <c r="T1" s="65" t="s">
+      <c r="T1" s="51" t="s">
         <v>19</v>
       </c>
-      <c r="U1" s="66" t="s">
+      <c r="U1" s="52" t="s">
         <v>20</v>
       </c>
       <c r="V1" s="37"/>
     </row>
-    <row r="2" spans="1:30" ht="81">
+    <row r="2" spans="1:22" ht="45" x14ac:dyDescent="0.25">
       <c r="A2" s="39" t="s">
         <v>21</v>
       </c>
@@ -1245,516 +1273,390 @@
         <v>22</v>
       </c>
       <c r="C2" s="6"/>
-      <c r="D2" s="40">
+      <c r="D2" s="57">
         <v>124570.12</v>
       </c>
-      <c r="E2" s="41" t="s">
+      <c r="E2" s="58" t="s">
         <v>23</v>
       </c>
-      <c r="F2" s="1" t="s">
+      <c r="F2" s="59" t="s">
         <v>24</v>
       </c>
-      <c r="G2" s="9">
+      <c r="G2" s="60">
         <v>0</v>
       </c>
-      <c r="H2" s="8">
+      <c r="H2" s="74">
         <v>1500</v>
       </c>
-      <c r="I2" s="1" t="s">
+      <c r="I2" s="59" t="s">
         <v>25</v>
       </c>
-      <c r="J2" s="42" t="s">
+      <c r="J2" s="61" t="s">
         <v>26</v>
       </c>
       <c r="K2" s="6"/>
-      <c r="L2" s="67" t="s">
+      <c r="L2" s="53" t="s">
         <v>27</v>
       </c>
-      <c r="M2" s="60"/>
-      <c r="N2" s="68" t="s">
+      <c r="M2" s="46"/>
+      <c r="N2" s="54" t="s">
         <v>28</v>
       </c>
-      <c r="O2" s="60"/>
-      <c r="P2" s="60"/>
-      <c r="Q2" s="60"/>
-      <c r="R2" s="60"/>
-      <c r="S2" s="69" t="s">
+      <c r="O2" s="46"/>
+      <c r="P2" s="46"/>
+      <c r="Q2" s="46"/>
+      <c r="R2" s="46"/>
+      <c r="S2" s="55" t="s">
         <v>29</v>
       </c>
-      <c r="T2" s="60"/>
-      <c r="U2" s="69"/>
-      <c r="X2" s="6" t="s">
+      <c r="T2" s="46"/>
+      <c r="U2" s="55"/>
+    </row>
+    <row r="3" spans="1:22" ht="45" x14ac:dyDescent="0.25">
+      <c r="A3" s="40" t="s">
+        <v>30</v>
+      </c>
+      <c r="B3" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C3" s="6"/>
+      <c r="D3" s="57">
+        <v>518743.75</v>
+      </c>
+      <c r="E3" s="58" t="s">
+        <v>32</v>
+      </c>
+      <c r="F3" s="62" t="s">
+        <v>33</v>
+      </c>
+      <c r="G3" s="60">
+        <v>0</v>
+      </c>
+      <c r="H3" s="74">
+        <v>0.2</v>
+      </c>
+      <c r="I3" s="59" t="s">
+        <v>25</v>
+      </c>
+      <c r="J3" s="61" t="s">
+        <v>34</v>
+      </c>
+      <c r="K3" s="6"/>
+      <c r="L3" s="53" t="s">
         <v>27</v>
       </c>
-      <c r="Y2" s="6"/>
-      <c r="Z2" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="AA2" s="6" t="s">
+      <c r="M3" s="46"/>
+      <c r="N3" s="54" t="s">
+        <v>35</v>
+      </c>
+      <c r="O3" s="46"/>
+      <c r="P3" s="46"/>
+      <c r="Q3" s="46"/>
+      <c r="R3" s="46"/>
+      <c r="S3" s="55" t="s">
+        <v>29</v>
+      </c>
+      <c r="T3" s="46"/>
+      <c r="U3" s="55"/>
+    </row>
+    <row r="4" spans="1:22" ht="45" x14ac:dyDescent="0.25">
+      <c r="A4" s="41" t="s">
+        <v>36</v>
+      </c>
+      <c r="B4" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="C4" s="6"/>
+      <c r="D4" s="57">
+        <v>246584.79</v>
+      </c>
+      <c r="E4" s="58" t="s">
+        <v>23</v>
+      </c>
+      <c r="F4" s="63" t="s">
+        <v>24</v>
+      </c>
+      <c r="G4" s="60">
+        <v>0</v>
+      </c>
+      <c r="H4" s="74">
+        <v>100</v>
+      </c>
+      <c r="I4" s="59" t="s">
+        <v>25</v>
+      </c>
+      <c r="J4" s="61" t="s">
+        <v>34</v>
+      </c>
+      <c r="K4" s="6"/>
+      <c r="L4" s="53" t="s">
+        <v>27</v>
+      </c>
+      <c r="M4" s="46"/>
+      <c r="N4" s="54" t="s">
         <v>28</v>
       </c>
-      <c r="AB2" s="6" t="s">
+      <c r="O4" s="46"/>
+      <c r="P4" s="46"/>
+      <c r="Q4" s="46"/>
+      <c r="R4" s="46"/>
+      <c r="S4" s="55" t="s">
+        <v>29</v>
+      </c>
+      <c r="T4" s="46"/>
+      <c r="U4" s="55"/>
+    </row>
+    <row r="5" spans="1:22" ht="45" x14ac:dyDescent="0.25">
+      <c r="A5" s="42" t="s">
+        <v>38</v>
+      </c>
+      <c r="B5" s="43" t="s">
+        <v>39</v>
+      </c>
+      <c r="C5" s="4"/>
+      <c r="D5" s="64">
+        <v>186391.71</v>
+      </c>
+      <c r="E5" s="58" t="s">
         <v>23</v>
       </c>
-      <c r="AC2" s="60"/>
-      <c r="AD2" s="6"/>
-    </row>
-    <row r="3" spans="1:30" ht="81">
-      <c r="A3" s="43" t="s">
-        <v>31</v>
-      </c>
-      <c r="B3" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="C3" s="6"/>
-      <c r="D3" s="40">
-        <v>518743.75</v>
-      </c>
-      <c r="E3" s="41" t="s">
-        <v>33</v>
-      </c>
-      <c r="F3" s="6" t="s">
+      <c r="F5" s="63" t="s">
+        <v>24</v>
+      </c>
+      <c r="G5" s="60">
+        <v>0</v>
+      </c>
+      <c r="H5" s="74">
+        <v>1200</v>
+      </c>
+      <c r="I5" s="59" t="s">
+        <v>25</v>
+      </c>
+      <c r="J5" s="61" t="s">
         <v>34</v>
       </c>
-      <c r="G3" s="9">
+      <c r="K5" s="6"/>
+      <c r="L5" s="53" t="s">
+        <v>27</v>
+      </c>
+      <c r="M5" s="46"/>
+      <c r="N5" s="54" t="s">
+        <v>28</v>
+      </c>
+      <c r="O5" s="46"/>
+      <c r="P5" s="46"/>
+      <c r="Q5" s="46"/>
+      <c r="R5" s="46"/>
+      <c r="S5" s="55" t="s">
+        <v>29</v>
+      </c>
+      <c r="T5" s="46"/>
+      <c r="U5" s="55"/>
+    </row>
+    <row r="6" spans="1:22" ht="45" x14ac:dyDescent="0.25">
+      <c r="A6" s="42" t="s">
+        <v>40</v>
+      </c>
+      <c r="B6" s="43" t="s">
+        <v>41</v>
+      </c>
+      <c r="C6" s="4"/>
+      <c r="D6" s="64">
+        <v>149770.73000000001</v>
+      </c>
+      <c r="E6" s="58" t="s">
+        <v>23</v>
+      </c>
+      <c r="F6" s="63" t="s">
+        <v>24</v>
+      </c>
+      <c r="G6" s="60">
         <v>0</v>
       </c>
-      <c r="H3" s="9">
-        <v>0.2</v>
-      </c>
-      <c r="I3" s="1" t="s">
+      <c r="H6" s="74">
         <v>25</v>
       </c>
-      <c r="J3" s="42" t="s">
-        <v>35</v>
-      </c>
-      <c r="K3" s="6"/>
-      <c r="L3" s="67" t="s">
+      <c r="I6" s="59" t="s">
+        <v>25</v>
+      </c>
+      <c r="J6" s="61" t="s">
+        <v>34</v>
+      </c>
+      <c r="K6" s="6"/>
+      <c r="L6" s="53" t="s">
         <v>27</v>
       </c>
-      <c r="M3" s="60"/>
-      <c r="N3" s="68" t="s">
-        <v>36</v>
-      </c>
-      <c r="O3" s="60"/>
-      <c r="P3" s="60"/>
-      <c r="Q3" s="60"/>
-      <c r="R3" s="60"/>
-      <c r="S3" s="69" t="s">
+      <c r="M6" s="46"/>
+      <c r="N6" s="54" t="s">
+        <v>28</v>
+      </c>
+      <c r="O6" s="46"/>
+      <c r="P6" s="46"/>
+      <c r="Q6" s="46"/>
+      <c r="R6" s="46"/>
+      <c r="S6" s="55" t="s">
         <v>29</v>
       </c>
-      <c r="T3" s="60"/>
-      <c r="U3" s="69"/>
-      <c r="X3" s="6" t="s">
+      <c r="T6" s="46"/>
+      <c r="U6" s="55"/>
+    </row>
+    <row r="7" spans="1:22" ht="45" x14ac:dyDescent="0.25">
+      <c r="A7" s="42" t="s">
+        <v>42</v>
+      </c>
+      <c r="B7" s="44" t="s">
+        <v>43</v>
+      </c>
+      <c r="C7" s="7"/>
+      <c r="D7" s="57">
+        <v>118418</v>
+      </c>
+      <c r="E7" s="58" t="s">
+        <v>23</v>
+      </c>
+      <c r="F7" s="63" t="s">
+        <v>24</v>
+      </c>
+      <c r="G7" s="60">
+        <v>0</v>
+      </c>
+      <c r="H7" s="74">
+        <v>60</v>
+      </c>
+      <c r="I7" s="59" t="s">
+        <v>25</v>
+      </c>
+      <c r="J7" s="61" t="s">
+        <v>34</v>
+      </c>
+      <c r="K7" s="6"/>
+      <c r="L7" s="53" t="s">
         <v>27</v>
       </c>
-      <c r="Y3" s="6"/>
-      <c r="Z3" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="AA3" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="AB3" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="AC3" s="60"/>
-      <c r="AD3" s="6"/>
-    </row>
-    <row r="4" spans="1:30" ht="81">
-      <c r="A4" s="44" t="s">
+      <c r="M7" s="46"/>
+      <c r="N7" s="54" t="s">
+        <v>28</v>
+      </c>
+      <c r="O7" s="46"/>
+      <c r="P7" s="46"/>
+      <c r="Q7" s="46"/>
+      <c r="R7" s="46"/>
+      <c r="S7" s="55" t="s">
+        <v>29</v>
+      </c>
+      <c r="T7" s="46"/>
+      <c r="U7" s="55"/>
+    </row>
+    <row r="8" spans="1:22" ht="45" x14ac:dyDescent="0.25">
+      <c r="A8" s="39" t="s">
         <v>38</v>
       </c>
-      <c r="B4" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="C4" s="6"/>
-      <c r="D4" s="40">
-        <v>246584.79</v>
-      </c>
-      <c r="E4" s="41" t="s">
-        <v>23</v>
-      </c>
-      <c r="F4" s="51" t="s">
+      <c r="B8" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="C8" s="6"/>
+      <c r="D8" s="65">
+        <v>62161.5</v>
+      </c>
+      <c r="E8" s="66" t="s">
+        <v>45</v>
+      </c>
+      <c r="F8" s="63" t="s">
         <v>24</v>
       </c>
-      <c r="G4" s="9">
+      <c r="G8" s="67">
         <v>0</v>
       </c>
-      <c r="H4" s="9">
-        <v>100</v>
-      </c>
-      <c r="I4" s="1" t="s">
+      <c r="H8" s="75">
+        <v>5000</v>
+      </c>
+      <c r="I8" s="59" t="s">
         <v>25</v>
       </c>
-      <c r="J4" s="42" t="s">
-        <v>35</v>
-      </c>
-      <c r="K4" s="6"/>
-      <c r="L4" s="67" t="s">
+      <c r="J8" s="61" t="s">
+        <v>34</v>
+      </c>
+      <c r="K8" s="6"/>
+      <c r="L8" s="53" t="s">
         <v>27</v>
       </c>
-      <c r="M4" s="60"/>
-      <c r="N4" s="68" t="s">
+      <c r="M8" s="46"/>
+      <c r="N8" s="54" t="s">
         <v>28</v>
       </c>
-      <c r="O4" s="60"/>
-      <c r="P4" s="60"/>
-      <c r="Q4" s="60"/>
-      <c r="R4" s="60"/>
-      <c r="S4" s="69" t="s">
-        <v>29</v>
-      </c>
-      <c r="T4" s="60"/>
-      <c r="U4" s="69"/>
-      <c r="X4" s="6" t="s">
+      <c r="O8" s="46"/>
+      <c r="P8" s="46"/>
+      <c r="Q8" s="46"/>
+      <c r="R8" s="46"/>
+      <c r="S8" s="55"/>
+      <c r="T8" s="46"/>
+      <c r="U8" s="55"/>
+    </row>
+    <row r="9" spans="1:22" ht="108.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="45" t="s">
+        <v>46</v>
+      </c>
+      <c r="B9" s="32" t="s">
+        <v>47</v>
+      </c>
+      <c r="C9" s="32"/>
+      <c r="D9" s="68">
+        <v>6268828.7999999998</v>
+      </c>
+      <c r="E9" s="66" t="s">
+        <v>48</v>
+      </c>
+      <c r="F9" s="63" t="s">
+        <v>24</v>
+      </c>
+      <c r="G9" s="67">
+        <v>0</v>
+      </c>
+      <c r="H9" s="75">
+        <v>2080000</v>
+      </c>
+      <c r="I9" s="59" t="s">
+        <v>49</v>
+      </c>
+      <c r="J9" s="61" t="s">
+        <v>34</v>
+      </c>
+      <c r="K9" s="32"/>
+      <c r="L9" s="53" t="s">
         <v>27</v>
       </c>
-      <c r="Y4" s="6"/>
-      <c r="Z4" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="AA4" s="6" t="s">
+      <c r="M9" s="46"/>
+      <c r="N9" s="54" t="s">
         <v>28</v>
       </c>
-      <c r="AB4" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="AC4" s="60"/>
-      <c r="AD4" s="6"/>
-    </row>
-    <row r="5" spans="1:30" ht="81">
-      <c r="A5" s="45" t="s">
-        <v>40</v>
-      </c>
-      <c r="B5" s="46" t="s">
-        <v>41</v>
-      </c>
-      <c r="C5" s="4"/>
-      <c r="D5" s="47">
-        <v>186391.71</v>
-      </c>
-      <c r="E5" s="41" t="s">
-        <v>23</v>
-      </c>
-      <c r="F5" s="51" t="s">
-        <v>24</v>
-      </c>
-      <c r="G5" s="9">
-        <v>0</v>
-      </c>
-      <c r="H5" s="9">
-        <v>1200</v>
-      </c>
-      <c r="I5" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="J5" s="42" t="s">
-        <v>35</v>
-      </c>
-      <c r="K5" s="6"/>
-      <c r="L5" s="67" t="s">
-        <v>27</v>
-      </c>
-      <c r="M5" s="60"/>
-      <c r="N5" s="68" t="s">
-        <v>28</v>
-      </c>
-      <c r="O5" s="60"/>
-      <c r="P5" s="60"/>
-      <c r="Q5" s="60"/>
-      <c r="R5" s="60"/>
-      <c r="S5" s="69" t="s">
-        <v>29</v>
-      </c>
-      <c r="T5" s="60"/>
-      <c r="U5" s="69"/>
-      <c r="X5" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="Y5" s="6"/>
-      <c r="Z5" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="AA5" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="AB5" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="AC5" s="60"/>
-      <c r="AD5" s="6"/>
-    </row>
-    <row r="6" spans="1:30" ht="81">
-      <c r="A6" s="45" t="s">
-        <v>42</v>
-      </c>
-      <c r="B6" s="46" t="s">
-        <v>43</v>
-      </c>
-      <c r="C6" s="4"/>
-      <c r="D6" s="47">
-        <v>149770.73000000001</v>
-      </c>
-      <c r="E6" s="41" t="s">
-        <v>23</v>
-      </c>
-      <c r="F6" s="51" t="s">
-        <v>24</v>
-      </c>
-      <c r="G6" s="9">
-        <v>0</v>
-      </c>
-      <c r="H6" s="9">
-        <v>25</v>
-      </c>
-      <c r="I6" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="J6" s="42" t="s">
-        <v>35</v>
-      </c>
-      <c r="K6" s="6"/>
-      <c r="L6" s="67" t="s">
-        <v>27</v>
-      </c>
-      <c r="M6" s="60"/>
-      <c r="N6" s="68" t="s">
-        <v>28</v>
-      </c>
-      <c r="O6" s="60"/>
-      <c r="P6" s="60"/>
-      <c r="Q6" s="60"/>
-      <c r="R6" s="60"/>
-      <c r="S6" s="69" t="s">
-        <v>29</v>
-      </c>
-      <c r="T6" s="60"/>
-      <c r="U6" s="69"/>
-      <c r="X6" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="Y6" s="6"/>
-      <c r="Z6" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="AA6" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="AB6" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="AC6" s="60"/>
-      <c r="AD6" s="6"/>
-    </row>
-    <row r="7" spans="1:30" ht="81">
-      <c r="A7" s="45" t="s">
-        <v>44</v>
-      </c>
-      <c r="B7" s="48" t="s">
-        <v>45</v>
-      </c>
-      <c r="C7" s="7"/>
-      <c r="D7" s="40">
-        <v>118418</v>
-      </c>
-      <c r="E7" s="41" t="s">
-        <v>23</v>
-      </c>
-      <c r="F7" s="51" t="s">
-        <v>24</v>
-      </c>
-      <c r="G7" s="9">
-        <v>0</v>
-      </c>
-      <c r="H7" s="9">
-        <v>60</v>
-      </c>
-      <c r="I7" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="J7" s="42" t="s">
-        <v>35</v>
-      </c>
-      <c r="K7" s="6"/>
-      <c r="L7" s="67" t="s">
-        <v>27</v>
-      </c>
-      <c r="M7" s="60"/>
-      <c r="N7" s="68" t="s">
-        <v>28</v>
-      </c>
-      <c r="O7" s="60"/>
-      <c r="P7" s="60"/>
-      <c r="Q7" s="60"/>
-      <c r="R7" s="60"/>
-      <c r="S7" s="69" t="s">
-        <v>29</v>
-      </c>
-      <c r="T7" s="60"/>
-      <c r="U7" s="69"/>
-      <c r="X7" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="Y7" s="6"/>
-      <c r="Z7" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="AA7" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="AB7" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="AC7" s="60"/>
-      <c r="AD7" s="6"/>
-    </row>
-    <row r="8" spans="1:30" ht="81">
-      <c r="A8" s="39" t="s">
-        <v>40</v>
-      </c>
-      <c r="B8" s="6" t="s">
-        <v>46</v>
-      </c>
-      <c r="C8" s="6"/>
-      <c r="D8" s="49">
-        <v>62161.5</v>
-      </c>
-      <c r="E8" s="50" t="s">
-        <v>47</v>
-      </c>
-      <c r="F8" s="51" t="s">
-        <v>24</v>
-      </c>
-      <c r="G8" s="11">
-        <v>0</v>
-      </c>
-      <c r="H8" s="11">
-        <v>5000</v>
-      </c>
-      <c r="I8" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="J8" s="42" t="s">
-        <v>35</v>
-      </c>
-      <c r="K8" s="6"/>
-      <c r="L8" s="67" t="s">
-        <v>27</v>
-      </c>
-      <c r="M8" s="60"/>
-      <c r="N8" s="68" t="s">
-        <v>28</v>
-      </c>
-      <c r="O8" s="60"/>
-      <c r="P8" s="60"/>
-      <c r="Q8" s="60"/>
-      <c r="R8" s="60"/>
-      <c r="S8" s="69"/>
-      <c r="T8" s="60"/>
-      <c r="U8" s="69"/>
-      <c r="X8" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="Y8" s="6"/>
-      <c r="Z8" s="6"/>
-      <c r="AA8" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="AB8" s="6" t="s">
-        <v>48</v>
-      </c>
-      <c r="AC8" s="60"/>
-      <c r="AD8" s="6"/>
-    </row>
-    <row r="9" spans="1:30" ht="52.5" customHeight="1">
-      <c r="A9" s="52" t="s">
-        <v>49</v>
-      </c>
-      <c r="B9" s="32" t="s">
+      <c r="O9" s="46"/>
+      <c r="P9" s="46" t="s">
         <v>50</v>
       </c>
-      <c r="C9" s="32"/>
-      <c r="D9" s="53">
-        <v>6268828.7999999998</v>
-      </c>
-      <c r="E9" s="54" t="s">
-        <v>51</v>
-      </c>
-      <c r="F9" s="55" t="s">
-        <v>24</v>
-      </c>
-      <c r="G9" s="56">
-        <v>0</v>
-      </c>
-      <c r="H9" s="56">
-        <v>9000000</v>
-      </c>
-      <c r="I9" s="57" t="s">
-        <v>52</v>
-      </c>
-      <c r="J9" s="58" t="s">
-        <v>35</v>
-      </c>
-      <c r="K9" s="32"/>
-      <c r="L9" s="67" t="s">
-        <v>27</v>
-      </c>
-      <c r="M9" s="60"/>
-      <c r="N9" s="68" t="s">
-        <v>28</v>
-      </c>
-      <c r="O9" s="60"/>
-      <c r="P9" s="60" t="s">
-        <v>53</v>
-      </c>
-      <c r="Q9" s="60"/>
-      <c r="R9" s="60"/>
-      <c r="S9" s="69"/>
-      <c r="T9" s="60"/>
-      <c r="U9" s="69"/>
-      <c r="X9" s="32" t="s">
-        <v>27</v>
-      </c>
-      <c r="Y9" s="59" t="s">
-        <v>54</v>
-      </c>
-      <c r="Z9" s="32"/>
-      <c r="AA9" s="32" t="s">
-        <v>28</v>
-      </c>
-      <c r="AB9" s="32" t="s">
-        <v>37</v>
-      </c>
-      <c r="AC9" s="60"/>
-      <c r="AD9" s="32" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="10" spans="1:30">
+      <c r="Q9" s="46"/>
+      <c r="R9" s="46"/>
+      <c r="S9" s="55"/>
+      <c r="T9" s="46"/>
+      <c r="U9" s="55"/>
+    </row>
+    <row r="10" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A10" s="26"/>
-      <c r="J10" s="31"/>
-    </row>
-    <row r="11" spans="1:30">
+      <c r="J10" s="72"/>
+    </row>
+    <row r="11" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A11" s="26"/>
-      <c r="J11" s="31"/>
+      <c r="J11" s="72"/>
     </row>
   </sheetData>
-  <dataValidations count="11">
+  <dataValidations count="9">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="Q2:Q9" xr:uid="{F6F28849-87EB-4F9A-AB3E-00CBE75897DB}">
       <formula1>"NDC Support, National Strategy, Legal Framework,Incentives and Support, Government Capacity-Building, Carbon Pricing and Monitoring, Financing Model, Business Model"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AD2:AD9 P2:P9" xr:uid="{880E93DE-C740-4A5E-8262-14AAD00BAF7E}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="P2:P9" xr:uid="{880E93DE-C740-4A5E-8262-14AAD00BAF7E}">
       <formula1>"AMP, PUDC, Solar4Health, Action Opportunities, Italy UNDP Energy Partnership"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AB2:AB9" xr:uid="{47A900B3-8194-4117-9E79-9461B6F4ABA9}">
-      <formula1>"Electricity Access, Energy Efficiency, Clean Cooking, Renewable Energy"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AA2:AA9 N2:N9" xr:uid="{1011BCA5-28B7-4115-B450-DDC676C3F402}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="N2:N9" xr:uid="{1011BCA5-28B7-4115-B450-DDC676C3F402}">
       <formula1>"Accelerating just energy transition, Close the gap on energy access, Scale up energy finance"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AC2:AC9" xr:uid="{61134F44-1E6D-47C3-BD9E-D64F77296A90}">
-      <formula1>"Tier 1, Tier 2, Tier 3"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="O2:O9" xr:uid="{14FB2570-6F95-44D5-A173-4519435340E6}">
       <formula1>"Electricity Access, Energy Efficiency, Clean Cooking, Renewable Energy, Overall"</formula1>
@@ -1799,7 +1701,7 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:U11"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15.75"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="46.5703125" style="23" customWidth="1"/>
     <col min="2" max="2" width="54.140625" style="23" customWidth="1"/>
@@ -1817,7 +1719,7 @@
     <col min="14" max="16384" width="8.85546875" style="23"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" ht="16.5">
+    <row r="1" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A1" s="12" t="s">
         <v>0</v>
       </c>
@@ -1852,10 +1754,10 @@
         <v>10</v>
       </c>
       <c r="L1" s="37" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="M1" s="37" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="N1" s="37"/>
       <c r="O1" s="37" t="s">
@@ -1876,16 +1778,16 @@
       <c r="T1" s="37"/>
       <c r="U1" s="37"/>
     </row>
-    <row r="2" spans="1:21" ht="16.5">
+    <row r="2" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A2" s="17" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="B2" s="6" t="s">
         <v>22</v>
       </c>
       <c r="C2" s="14"/>
       <c r="D2" s="18" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="E2" s="22" t="s">
         <v>23</v>
@@ -1916,22 +1818,22 @@
         <v>23</v>
       </c>
     </row>
-    <row r="3" spans="1:21" ht="16.5">
+    <row r="3" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A3" s="19" t="s">
+        <v>30</v>
+      </c>
+      <c r="B3" s="14" t="s">
         <v>31</v>
-      </c>
-      <c r="B3" s="14" t="s">
-        <v>32</v>
       </c>
       <c r="C3" s="14"/>
       <c r="D3" s="18">
         <v>518743.75</v>
       </c>
       <c r="E3" s="22" t="s">
+        <v>32</v>
+      </c>
+      <c r="F3" s="6" t="s">
         <v>33</v>
-      </c>
-      <c r="F3" s="6" t="s">
-        <v>34</v>
       </c>
       <c r="G3" s="9">
         <v>0</v>
@@ -1943,25 +1845,25 @@
         <v>25</v>
       </c>
       <c r="J3" s="33" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="K3" s="14"/>
       <c r="L3" s="23" t="s">
         <v>27</v>
       </c>
       <c r="O3" s="23" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="P3" s="23" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="4" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A4" s="20" t="s">
+        <v>56</v>
+      </c>
+      <c r="B4" s="14" t="s">
         <v>37</v>
-      </c>
-    </row>
-    <row r="4" spans="1:21" ht="16.5">
-      <c r="A4" s="20" t="s">
-        <v>59</v>
-      </c>
-      <c r="B4" s="14" t="s">
-        <v>39</v>
       </c>
       <c r="C4" s="14"/>
       <c r="D4" s="18">
@@ -1983,7 +1885,7 @@
         <v>25</v>
       </c>
       <c r="J4" s="33" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="K4" s="14"/>
       <c r="L4" s="23" t="s">
@@ -1996,12 +1898,12 @@
         <v>23</v>
       </c>
     </row>
-    <row r="5" spans="1:21" ht="16.5">
+    <row r="5" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C5" s="4"/>
       <c r="D5" s="5">
@@ -2023,7 +1925,7 @@
         <v>25</v>
       </c>
       <c r="J5" s="33" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="K5" s="14"/>
       <c r="L5" s="23" t="s">
@@ -2036,12 +1938,12 @@
         <v>23</v>
       </c>
     </row>
-    <row r="6" spans="1:21" ht="16.5">
+    <row r="6" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="C6" s="4"/>
       <c r="D6" s="5">
@@ -2063,7 +1965,7 @@
         <v>25</v>
       </c>
       <c r="J6" s="33" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="K6" s="14"/>
       <c r="L6" s="23" t="s">
@@ -2076,12 +1978,12 @@
         <v>23</v>
       </c>
     </row>
-    <row r="7" spans="1:21" ht="16.5">
+    <row r="7" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B7" s="15" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="C7" s="7"/>
       <c r="D7" s="18">
@@ -2103,7 +2005,7 @@
         <v>25</v>
       </c>
       <c r="J7" s="33" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="K7" s="14"/>
       <c r="L7" s="23" t="s">
@@ -2116,19 +2018,19 @@
         <v>23</v>
       </c>
     </row>
-    <row r="8" spans="1:21" ht="16.5">
+    <row r="8" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A8" s="17" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="B8" s="14" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="C8" s="14"/>
       <c r="D8" s="21">
         <v>62161.5</v>
       </c>
       <c r="E8" s="24" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="F8" s="36" t="s">
         <v>24</v>
@@ -2143,7 +2045,7 @@
         <v>25</v>
       </c>
       <c r="J8" s="33" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="K8" s="14"/>
       <c r="L8" s="23" t="s">
@@ -2153,22 +2055,22 @@
         <v>28</v>
       </c>
       <c r="P8" s="23" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="9" spans="1:21" ht="52.5" customHeight="1">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="9" spans="1:21" ht="52.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="17" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="B9" s="14" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="C9" s="14"/>
       <c r="D9" s="25">
         <v>6268828.7999999998</v>
       </c>
       <c r="E9" s="24" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="F9" s="36" t="s">
         <v>24</v>
@@ -2180,33 +2082,33 @@
         <v>9000000</v>
       </c>
       <c r="I9" s="1" t="s">
-        <v>52</v>
+        <v>63</v>
       </c>
       <c r="J9" s="33" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="K9" s="14"/>
       <c r="L9" s="23" t="s">
         <v>27</v>
       </c>
       <c r="M9" s="38" t="s">
-        <v>54</v>
+        <v>64</v>
       </c>
       <c r="O9" s="23" t="s">
         <v>28</v>
       </c>
       <c r="P9" s="23" t="s">
-        <v>37</v>
+        <v>55</v>
       </c>
       <c r="Q9" s="23" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="10" spans="1:21">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="10" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A10" s="26"/>
       <c r="J10" s="31"/>
     </row>
-    <row r="11" spans="1:21">
+    <row r="11" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A11" s="26"/>
       <c r="J11" s="31"/>
     </row>
@@ -2240,7 +2142,7 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:L11"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15.75"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="46.5703125" style="23" customWidth="1"/>
     <col min="2" max="2" width="54.140625" style="23" customWidth="1"/>
@@ -2256,7 +2158,7 @@
     <col min="12" max="16384" width="8.85546875" style="23"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" ht="16.5">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A1" s="12" t="s">
         <v>0</v>
       </c>
@@ -2291,16 +2193,16 @@
         <v>65</v>
       </c>
     </row>
-    <row r="2" spans="1:12" ht="48.75">
+    <row r="2" spans="1:12" ht="47.25" x14ac:dyDescent="0.25">
       <c r="A2" s="17" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="B2" s="6" t="s">
         <v>22</v>
       </c>
       <c r="C2" s="14"/>
       <c r="D2" s="18" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="E2" s="22" t="s">
         <v>23</v>
@@ -2327,22 +2229,22 @@
         <v>69</v>
       </c>
     </row>
-    <row r="3" spans="1:12" ht="16.5">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A3" s="19" t="s">
+        <v>30</v>
+      </c>
+      <c r="B3" s="14" t="s">
         <v>31</v>
-      </c>
-      <c r="B3" s="14" t="s">
-        <v>32</v>
       </c>
       <c r="C3" s="14"/>
       <c r="D3" s="18">
         <v>518743.75</v>
       </c>
       <c r="E3" s="22" t="s">
+        <v>32</v>
+      </c>
+      <c r="F3" s="6" t="s">
         <v>33</v>
-      </c>
-      <c r="F3" s="6" t="s">
-        <v>34</v>
       </c>
       <c r="G3" s="9">
         <v>0</v>
@@ -2354,16 +2256,16 @@
         <v>25</v>
       </c>
       <c r="J3" s="33" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="K3" s="14"/>
     </row>
-    <row r="4" spans="1:12" ht="16.5">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A4" s="20" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="B4" s="14" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C4" s="14"/>
       <c r="D4" s="18">
@@ -2373,7 +2275,7 @@
         <v>23</v>
       </c>
       <c r="F4" s="6" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="G4" s="9">
         <v>0</v>
@@ -2385,16 +2287,16 @@
         <v>25</v>
       </c>
       <c r="J4" s="33" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="K4" s="14"/>
     </row>
-    <row r="5" spans="1:12" ht="32.25">
+    <row r="5" spans="1:12" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C5" s="4"/>
       <c r="D5" s="5">
@@ -2416,16 +2318,16 @@
         <v>25</v>
       </c>
       <c r="J5" s="33" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="K5" s="14"/>
     </row>
-    <row r="6" spans="1:12" ht="32.25">
+    <row r="6" spans="1:12" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="C6" s="4"/>
       <c r="D6" s="5">
@@ -2447,16 +2349,16 @@
         <v>25</v>
       </c>
       <c r="J6" s="33" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="K6" s="14"/>
     </row>
-    <row r="7" spans="1:12" ht="32.25">
+    <row r="7" spans="1:12" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B7" s="15" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="C7" s="7"/>
       <c r="D7" s="18">
@@ -2478,23 +2380,23 @@
         <v>25</v>
       </c>
       <c r="J7" s="33" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="K7" s="14"/>
     </row>
-    <row r="8" spans="1:12" ht="48.75">
+    <row r="8" spans="1:12" ht="47.25" x14ac:dyDescent="0.25">
       <c r="A8" s="17" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="B8" s="14" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="C8" s="14"/>
       <c r="D8" s="21">
         <v>62161.5</v>
       </c>
       <c r="E8" s="24" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="F8" s="6" t="s">
         <v>75</v>
@@ -2509,23 +2411,23 @@
         <v>25</v>
       </c>
       <c r="J8" s="33" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="K8" s="14"/>
     </row>
-    <row r="9" spans="1:12" ht="52.5" customHeight="1">
+    <row r="9" spans="1:12" ht="52.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="17" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="B9" s="14" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="C9" s="14"/>
       <c r="D9" s="25">
         <v>6268828.7999999998</v>
       </c>
       <c r="E9" s="24" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="F9" s="34" t="s">
         <v>76</v>
@@ -2537,18 +2439,18 @@
         <v>77</v>
       </c>
       <c r="I9" s="1" t="s">
-        <v>52</v>
+        <v>63</v>
       </c>
       <c r="J9" s="33" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="K9" s="14"/>
     </row>
-    <row r="10" spans="1:12">
+    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A10" s="26"/>
       <c r="J10" s="31"/>
     </row>
-    <row r="11" spans="1:12">
+    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A11" s="26"/>
       <c r="J11" s="31"/>
     </row>
@@ -2562,185 +2464,185 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:B22"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" customHeight="1"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="30.42578125" customWidth="1"/>
     <col min="2" max="2" width="96" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2">
-      <c r="A1" s="61" t="s">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1" s="47" t="s">
         <v>4</v>
       </c>
-      <c r="B1" s="61" t="s">
+      <c r="B1" s="47" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="30.75">
-      <c r="A2" s="70" t="s">
+    <row r="2" spans="1:2" ht="30" x14ac:dyDescent="0.25">
+      <c r="A2" s="77" t="s">
         <v>23</v>
       </c>
-      <c r="B2" s="62" t="s">
+      <c r="B2" s="48" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="3" spans="1:2">
-      <c r="A3" s="70" t="s">
-        <v>33</v>
-      </c>
-      <c r="B3" s="62" t="s">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A3" s="77" t="s">
+        <v>32</v>
+      </c>
+      <c r="B3" s="48" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="4" spans="1:2" ht="30.75">
-      <c r="A4" s="70" t="s">
+    <row r="4" spans="1:2" ht="30" x14ac:dyDescent="0.25">
+      <c r="A4" s="77" t="s">
         <v>80</v>
       </c>
-      <c r="B4" s="62" t="s">
+      <c r="B4" s="48" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="5" spans="1:2">
-      <c r="A5" s="70" t="s">
+    <row r="5" spans="1:2" ht="30" x14ac:dyDescent="0.25">
+      <c r="A5" s="77" t="s">
         <v>82</v>
       </c>
-      <c r="B5" s="62" t="s">
+      <c r="B5" s="48" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="6" spans="1:2" ht="45.75">
-      <c r="A6" s="70" t="s">
-        <v>47</v>
-      </c>
-      <c r="B6" s="62" t="s">
+    <row r="6" spans="1:2" ht="60" x14ac:dyDescent="0.25">
+      <c r="A6" s="77" t="s">
+        <v>45</v>
+      </c>
+      <c r="B6" s="48" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="7" spans="1:2" ht="30.75">
-      <c r="A7" s="70" t="s">
-        <v>51</v>
-      </c>
-      <c r="B7" s="62" t="s">
+    <row r="7" spans="1:2" ht="30" x14ac:dyDescent="0.25">
+      <c r="A7" s="77" t="s">
+        <v>48</v>
+      </c>
+      <c r="B7" s="48" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="8" spans="1:2" ht="30.75">
-      <c r="A8" s="70" t="s">
+    <row r="8" spans="1:2" ht="30" x14ac:dyDescent="0.25">
+      <c r="A8" s="77" t="s">
         <v>86</v>
       </c>
-      <c r="B8" s="62" t="s">
+      <c r="B8" s="48" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="9" spans="1:2" ht="30.75">
-      <c r="A9" s="70" t="s">
+    <row r="9" spans="1:2" ht="30" x14ac:dyDescent="0.25">
+      <c r="A9" s="77" t="s">
         <v>88</v>
       </c>
-      <c r="B9" s="62" t="s">
+      <c r="B9" s="48" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="10" spans="1:2" ht="30.75">
-      <c r="A10" s="70" t="s">
+    <row r="10" spans="1:2" ht="30" x14ac:dyDescent="0.25">
+      <c r="A10" s="77" t="s">
         <v>90</v>
       </c>
-      <c r="B10" s="71" t="s">
+      <c r="B10" s="78" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="11" spans="1:2">
-      <c r="A11" s="70" t="s">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A11" s="77" t="s">
         <v>92</v>
       </c>
-      <c r="B11" s="71" t="s">
+      <c r="B11" s="78" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="12" spans="1:2" ht="30.75">
-      <c r="A12" s="70" t="s">
+    <row r="12" spans="1:2" ht="30" x14ac:dyDescent="0.25">
+      <c r="A12" s="77" t="s">
         <v>94</v>
       </c>
-      <c r="B12" s="62" t="s">
+      <c r="B12" s="48" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="13" spans="1:2">
-      <c r="A13" s="70" t="s">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A13" s="77" t="s">
         <v>96</v>
       </c>
-      <c r="B13" s="71" t="s">
+      <c r="B13" s="78" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="14" spans="1:2">
-      <c r="A14" s="70" t="s">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A14" s="77" t="s">
         <v>98</v>
       </c>
-      <c r="B14" s="71" t="s">
+      <c r="B14" s="78" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="15" spans="1:2">
-      <c r="A15" s="70" t="s">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A15" s="77" t="s">
         <v>100</v>
       </c>
-      <c r="B15" s="71" t="s">
+      <c r="B15" s="78" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="16" spans="1:2">
-      <c r="A16" s="70" t="s">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A16" s="77" t="s">
         <v>102</v>
       </c>
-      <c r="B16" s="71" t="s">
+      <c r="B16" s="78" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="17" spans="1:2">
-      <c r="A17" s="70" t="s">
+    <row r="17" spans="1:2" ht="30" x14ac:dyDescent="0.25">
+      <c r="A17" s="77" t="s">
         <v>104</v>
       </c>
-      <c r="B17" s="62" t="s">
+      <c r="B17" s="48" t="s">
         <v>105</v>
       </c>
     </row>
-    <row r="18" spans="1:2">
-      <c r="A18" s="70" t="s">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A18" s="77" t="s">
         <v>106</v>
       </c>
-      <c r="B18" s="71" t="s">
+      <c r="B18" s="78" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="19" spans="1:2" ht="45.75">
-      <c r="A19" s="70" t="s">
+    <row r="19" spans="1:2" ht="45" x14ac:dyDescent="0.25">
+      <c r="A19" s="77" t="s">
         <v>108</v>
       </c>
-      <c r="B19" s="71" t="s">
+      <c r="B19" s="78" t="s">
         <v>109</v>
       </c>
     </row>
-    <row r="20" spans="1:2">
-      <c r="A20" s="70" t="s">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A20" s="77" t="s">
         <v>110</v>
       </c>
-      <c r="B20" s="71" t="s">
+      <c r="B20" s="78" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="21" spans="1:2" ht="30.75">
-      <c r="A21" s="70" t="s">
+    <row r="21" spans="1:2" ht="30" x14ac:dyDescent="0.25">
+      <c r="A21" s="77" t="s">
         <v>19</v>
       </c>
-      <c r="B21" s="72" t="s">
+      <c r="B21" s="79" t="s">
         <v>112</v>
       </c>
     </row>
-    <row r="22" spans="1:2">
-      <c r="A22" s="70" t="s">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A22" s="77" t="s">
         <v>113</v>
       </c>
-      <c r="B22" s="71" t="s">
+      <c r="B22" s="78" t="s">
         <v>114</v>
       </c>
     </row>
@@ -2750,17 +2652,8 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010081A889D055969F449BCDADF9B8A9C0F0" ma:contentTypeVersion="17" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="0d2b1cfbe0bead55dc04bff20486709a">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="720239d0-7d3a-4257-bb40-a2a3b1409bb2" xmlns:ns3="fb9e4d32-074f-4c04-81ef-e811753dfd59" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="a3ed273af6605fa6a207dd3965c2d078" ns2:_="" ns3:_="">
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010081A889D055969F449BCDADF9B8A9C0F0" ma:contentTypeVersion="18" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="dd25160c21e587dbb66203dfb8c7aa52">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="720239d0-7d3a-4257-bb40-a2a3b1409bb2" xmlns:ns3="fb9e4d32-074f-4c04-81ef-e811753dfd59" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="05ccd5be12d50c438f9536854e894bcb" ns2:_="" ns3:_="">
     <xsd:import namespace="720239d0-7d3a-4257-bb40-a2a3b1409bb2"/>
     <xsd:import namespace="fb9e4d32-074f-4c04-81ef-e811753dfd59"/>
     <xsd:element name="properties">
@@ -2785,6 +2678,7 @@
                 <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
                 <xsd:element ref="ns3:TaxCatchAll" minOccurs="0"/>
                 <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
               </xsd:all>
             </xsd:complexType>
           </xsd:element>
@@ -2864,6 +2758,11 @@
     <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="24" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
       <xsd:simpleType>
         <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceSearchProperties" ma:index="25" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
       </xsd:simpleType>
     </xsd:element>
   </xsd:schema>
@@ -3007,6 +2906,15 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
@@ -3076,13 +2984,45 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4D06A8A7-AAD0-46D5-9E3E-4D298B186157}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{515924AF-006D-4410-90B0-C2B68DFD0A2C}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="720239d0-7d3a-4257-bb40-a2a3b1409bb2"/>
+    <ds:schemaRef ds:uri="fb9e4d32-074f-4c04-81ef-e811753dfd59"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8A9D3979-2075-4E7D-952D-E87544D07E21}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4D06A8A7-AAD0-46D5-9E3E-4D298B186157}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{84AEDBCE-AE29-4AA3-A5BD-B932231712F2}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{84AEDBCE-AE29-4AA3-A5BD-B932231712F2}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="720239d0-7d3a-4257-bb40-a2a3b1409bb2"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="fb9e4d32-074f-4c04-81ef-e811753dfd59"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/01_Input/00_CO Validation/South Sudan - Energy Projects.xlsx
+++ b/01_Input/00_CO Validation/South Sudan - Energy Projects.xlsx
@@ -257,7 +257,7 @@
       <protection locked="0" hidden="0"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="99">
+  <cellXfs count="100">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
@@ -508,12 +508,12 @@
     <xf numFmtId="164" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="164" fontId="7" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="4" fontId="7" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
@@ -521,6 +521,9 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="164" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="164" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -622,6 +625,86 @@
     </indexedColors>
   </colors>
 </styleSheet>
+</file>
+
+<file path=xl/comments/comment1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>CO validation update</author>
+  </authors>
+  <commentList>
+    <comment ref="K3" authorId="0" shapeId="0">
+      <text>
+        <t>[AUTO-ADDED] Project reports access/productive-use beneficiary numbers but no MW value. Please add installed capacity (MW) or confirm not applicable.</t>
+      </text>
+    </comment>
+    <comment ref="L3" authorId="0" shapeId="0">
+      <text>
+        <t>[AUTO-ADDED] Project reports access/productive-use beneficiary numbers but no MW value. Please add installed capacity (MW) or confirm not applicable.</t>
+      </text>
+    </comment>
+    <comment ref="K6" authorId="0" shapeId="0">
+      <text>
+        <t>[AUTO-ADDED] Project reports access/productive-use beneficiary numbers but no MW value. Please add installed capacity (MW) or confirm not applicable.</t>
+      </text>
+    </comment>
+    <comment ref="L6" authorId="0" shapeId="0">
+      <text>
+        <t>[AUTO-ADDED] Project reports access/productive-use beneficiary numbers but no MW value. Please add installed capacity (MW) or confirm not applicable.</t>
+      </text>
+    </comment>
+    <comment ref="K8" authorId="0" shapeId="0">
+      <text>
+        <t>[AUTO-ADDED] Project reports access/productive-use beneficiary numbers but no MW value. Please add installed capacity (MW) or confirm not applicable.</t>
+      </text>
+    </comment>
+    <comment ref="L8" authorId="0" shapeId="0">
+      <text>
+        <t>[AUTO-ADDED] Project reports access/productive-use beneficiary numbers but no MW value. Please add installed capacity (MW) or confirm not applicable.</t>
+      </text>
+    </comment>
+    <comment ref="K10" authorId="0" shapeId="0">
+      <text>
+        <t>[AUTO-ADDED] Project reports access/productive-use beneficiary numbers but no MW value. Please add installed capacity (MW) or confirm not applicable.</t>
+      </text>
+    </comment>
+    <comment ref="L10" authorId="0" shapeId="0">
+      <text>
+        <t>[AUTO-ADDED] Project reports access/productive-use beneficiary numbers but no MW value. Please add installed capacity (MW) or confirm not applicable.</t>
+      </text>
+    </comment>
+    <comment ref="K12" authorId="0" shapeId="0">
+      <text>
+        <t>[AUTO-ADDED] Project reports access/productive-use beneficiary numbers but no MW value. Please add installed capacity (MW) or confirm not applicable.</t>
+      </text>
+    </comment>
+    <comment ref="L12" authorId="0" shapeId="0">
+      <text>
+        <t>[AUTO-ADDED] Project reports access/productive-use beneficiary numbers but no MW value. Please add installed capacity (MW) or confirm not applicable.</t>
+      </text>
+    </comment>
+    <comment ref="K14" authorId="0" shapeId="0">
+      <text>
+        <t>[AUTO-ADDED] Project reports access/productive-use beneficiary numbers but no MW value. Please add installed capacity (MW) or confirm not applicable.</t>
+      </text>
+    </comment>
+    <comment ref="L14" authorId="0" shapeId="0">
+      <text>
+        <t>[AUTO-ADDED] Project reports access/productive-use beneficiary numbers but no MW value. Please add installed capacity (MW) or confirm not applicable.</t>
+      </text>
+    </comment>
+    <comment ref="K16" authorId="0" shapeId="0">
+      <text>
+        <t>[AUTO-ADDED] Project reports access/productive-use beneficiary numbers but no MW value. Please add installed capacity (MW) or confirm not applicable.</t>
+      </text>
+    </comment>
+    <comment ref="L16" authorId="0" shapeId="0">
+      <text>
+        <t>[AUTO-ADDED] Project reports access/productive-use beneficiary numbers but no MW value. Please add installed capacity (MW) or confirm not applicable.</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1150,15 +1233,11 @@
           <t>Installed capacity in MW for access/productive-use outputs</t>
         </is>
       </c>
-      <c r="K3" s="60" t="n">
+      <c r="K3" s="86" t="n">
         <v>0</v>
       </c>
-      <c r="L3" s="86" t="n"/>
-      <c r="M3" s="87" t="inlineStr">
-        <is>
-          <t>[AUTO-ADDED] Project reports access/productive-use beneficiary numbers but no MW value. Please add installed capacity (MW) or confirm not applicable.</t>
-        </is>
-      </c>
+      <c r="L3" s="87" t="n"/>
+      <c r="M3" s="59" t="n"/>
       <c r="N3" s="61" t="n"/>
       <c r="O3" s="6" t="n"/>
       <c r="P3" s="46" t="n"/>
@@ -1326,15 +1405,11 @@
           <t>Installed capacity in MW for access/productive-use outputs</t>
         </is>
       </c>
-      <c r="K6" s="60" t="n">
+      <c r="K6" s="86" t="n">
         <v>0</v>
       </c>
-      <c r="L6" s="86" t="n"/>
-      <c r="M6" s="87" t="inlineStr">
-        <is>
-          <t>[AUTO-ADDED] Project reports access/productive-use beneficiary numbers but no MW value. Please add installed capacity (MW) or confirm not applicable.</t>
-        </is>
-      </c>
+      <c r="L6" s="87" t="n"/>
+      <c r="M6" s="59" t="n"/>
       <c r="N6" s="61" t="n"/>
       <c r="O6" s="6" t="n"/>
       <c r="P6" s="46" t="n"/>
@@ -1434,15 +1509,11 @@
           <t>Installed capacity in MW for access/productive-use outputs</t>
         </is>
       </c>
-      <c r="K8" s="60" t="n">
+      <c r="K8" s="86" t="n">
         <v>0</v>
       </c>
-      <c r="L8" s="86" t="n"/>
-      <c r="M8" s="87" t="inlineStr">
-        <is>
-          <t>[AUTO-ADDED] Project reports access/productive-use beneficiary numbers but no MW value. Please add installed capacity (MW) or confirm not applicable.</t>
-        </is>
-      </c>
+      <c r="L8" s="87" t="n"/>
+      <c r="M8" s="59" t="n"/>
       <c r="N8" s="61" t="n"/>
       <c r="O8" s="6" t="n"/>
       <c r="P8" s="46" t="n"/>
@@ -1542,15 +1613,11 @@
           <t>Installed capacity in MW for access/productive-use outputs</t>
         </is>
       </c>
-      <c r="K10" s="60" t="n">
+      <c r="K10" s="86" t="n">
         <v>0</v>
       </c>
-      <c r="L10" s="86" t="n"/>
-      <c r="M10" s="87" t="inlineStr">
-        <is>
-          <t>[AUTO-ADDED] Project reports access/productive-use beneficiary numbers but no MW value. Please add installed capacity (MW) or confirm not applicable.</t>
-        </is>
-      </c>
+      <c r="L10" s="87" t="n"/>
+      <c r="M10" s="59" t="n"/>
       <c r="N10" s="61" t="n"/>
       <c r="O10" s="6" t="n"/>
       <c r="P10" s="46" t="n"/>
@@ -1650,15 +1717,11 @@
           <t>Installed capacity in MW for access/productive-use outputs</t>
         </is>
       </c>
-      <c r="K12" s="60" t="n">
+      <c r="K12" s="86" t="n">
         <v>0</v>
       </c>
-      <c r="L12" s="86" t="n"/>
-      <c r="M12" s="87" t="inlineStr">
-        <is>
-          <t>[AUTO-ADDED] Project reports access/productive-use beneficiary numbers but no MW value. Please add installed capacity (MW) or confirm not applicable.</t>
-        </is>
-      </c>
+      <c r="L12" s="87" t="n"/>
+      <c r="M12" s="59" t="n"/>
       <c r="N12" s="61" t="n"/>
       <c r="O12" s="6" t="n"/>
       <c r="P12" s="46" t="n"/>
@@ -1754,15 +1817,11 @@
           <t>Installed capacity in MW for access/productive-use outputs</t>
         </is>
       </c>
-      <c r="K14" s="67" t="n">
+      <c r="K14" s="91" t="n">
         <v>0</v>
       </c>
-      <c r="L14" s="91" t="n"/>
-      <c r="M14" s="87" t="inlineStr">
-        <is>
-          <t>[AUTO-ADDED] Project reports access/productive-use beneficiary numbers but no MW value. Please add installed capacity (MW) or confirm not applicable.</t>
-        </is>
-      </c>
+      <c r="L14" s="92" t="n"/>
+      <c r="M14" s="59" t="n"/>
       <c r="N14" s="61" t="n"/>
       <c r="O14" s="6" t="n"/>
       <c r="P14" s="46" t="n"/>
@@ -1787,13 +1846,13 @@
         </is>
       </c>
       <c r="C15" s="32" t="n"/>
-      <c r="D15" s="92" t="n">
+      <c r="D15" s="93" t="n">
         <v>6268828.8</v>
       </c>
-      <c r="E15" s="93" t="n"/>
-      <c r="F15" s="93" t="n"/>
-      <c r="G15" s="93" t="n"/>
-      <c r="H15" s="92" t="inlineStr">
+      <c r="E15" s="94" t="n"/>
+      <c r="F15" s="94" t="n"/>
+      <c r="G15" s="94" t="n"/>
+      <c r="H15" s="93" t="inlineStr">
         <is>
           <t>Non-VF</t>
         </is>
@@ -1847,11 +1906,11 @@
       <c r="A16" s="45" t="n"/>
       <c r="B16" s="32" t="n"/>
       <c r="C16" s="32" t="n"/>
-      <c r="D16" s="92" t="n"/>
-      <c r="E16" s="92" t="n"/>
-      <c r="F16" s="92" t="n"/>
-      <c r="G16" s="92" t="n"/>
-      <c r="H16" s="92" t="n"/>
+      <c r="D16" s="93" t="n"/>
+      <c r="E16" s="93" t="n"/>
+      <c r="F16" s="93" t="n"/>
+      <c r="G16" s="93" t="n"/>
+      <c r="H16" s="93" t="n"/>
       <c r="I16" s="66" t="inlineStr">
         <is>
           <t>Energy (MW added)</t>
@@ -1862,15 +1921,11 @@
           <t>Installed capacity in MW for access/productive-use outputs</t>
         </is>
       </c>
-      <c r="K16" s="67" t="n">
+      <c r="K16" s="91" t="n">
         <v>0</v>
       </c>
-      <c r="L16" s="91" t="n"/>
-      <c r="M16" s="87" t="inlineStr">
-        <is>
-          <t>[AUTO-ADDED] Project reports access/productive-use beneficiary numbers but no MW value. Please add installed capacity (MW) or confirm not applicable.</t>
-        </is>
-      </c>
+      <c r="L16" s="92" t="n"/>
+      <c r="M16" s="59" t="n"/>
       <c r="N16" s="61" t="n"/>
       <c r="O16" s="32" t="n"/>
       <c r="P16" s="46" t="n"/>
@@ -1892,7 +1947,7 @@
       <c r="N18" s="72" t="n"/>
     </row>
   </sheetData>
-  <dataValidations count="12">
+  <dataValidations count="10">
     <dataValidation sqref="Q2:Q9" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" type="list">
       <formula1>"NDC Support, National Strategy, Legal Framework,Incentives and Support, Government Capacity-Building, Carbon Pricing and Monitoring, Financing Model, Business Model"</formula1>
     </dataValidation>
@@ -1923,16 +1978,11 @@
     <dataValidation sqref="G2:G2001" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid Status" error="Select a status from the dropdown list." promptTitle="Status" prompt="Choose a project status." type="list">
       <formula1>"Pending,Approved,Active,Operationally Closed,Financially Closed,Suspended,Cancelled"</formula1>
     </dataValidation>
-    <dataValidation sqref="G2:G2001" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid Status" error="Select a status from the dropdown list." promptTitle="Status" prompt="Choose a project status." type="list">
-      <formula1>"Pending,Approved,Active,Operationally Closed,Financially Closed,Suspended,Cancelled"</formula1>
-    </dataValidation>
-    <dataValidation sqref="G2:G2001" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid Status" error="Select a status from the dropdown list." promptTitle="Status" prompt="Choose a project status." type="list">
-      <formula1>"Pending,Approved,Active,Operationally Closed,Financially Closed,Suspended,Cancelled"</formula1>
-    </dataValidation>
   </dataValidations>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="landscape" fitToHeight="0"/>
+  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>
 </file>
 
@@ -1948,7 +1998,7 @@
     <col width="46.5703125" customWidth="1" style="23" min="1" max="1"/>
     <col width="54.140625" customWidth="1" style="23" min="2" max="2"/>
     <col width="12" customWidth="1" style="23" min="3" max="3"/>
-    <col width="14.28515625" bestFit="1" customWidth="1" style="94" min="4" max="4"/>
+    <col width="14.28515625" bestFit="1" customWidth="1" style="95" min="4" max="4"/>
     <col width="21" bestFit="1" customWidth="1" style="28" min="5" max="5"/>
     <col width="46.85546875" customWidth="1" style="29" min="6" max="6"/>
     <col width="9.140625" bestFit="1" customWidth="1" style="28" min="7" max="7"/>
@@ -2068,7 +2118,7 @@
         </is>
       </c>
       <c r="C2" s="14" t="n"/>
-      <c r="D2" s="95" t="inlineStr">
+      <c r="D2" s="96" t="inlineStr">
         <is>
           <t>124, 570.12</t>
         </is>
@@ -2128,7 +2178,7 @@
         </is>
       </c>
       <c r="C3" s="14" t="n"/>
-      <c r="D3" s="95" t="n">
+      <c r="D3" s="96" t="n">
         <v>518743.75</v>
       </c>
       <c r="E3" s="22" t="inlineStr">
@@ -2186,7 +2236,7 @@
         </is>
       </c>
       <c r="C4" s="14" t="n"/>
-      <c r="D4" s="95" t="n">
+      <c r="D4" s="96" t="n">
         <v>246584.79</v>
       </c>
       <c r="E4" s="22" t="inlineStr">
@@ -2360,7 +2410,7 @@
         </is>
       </c>
       <c r="C7" s="7" t="n"/>
-      <c r="D7" s="95" t="n">
+      <c r="D7" s="96" t="n">
         <v>118418</v>
       </c>
       <c r="E7" s="22" t="inlineStr">
@@ -2476,7 +2526,7 @@
         </is>
       </c>
       <c r="C9" s="14" t="n"/>
-      <c r="D9" s="96" t="n">
+      <c r="D9" s="97" t="n">
         <v>6268828.8</v>
       </c>
       <c r="E9" s="24" t="inlineStr">
@@ -2576,7 +2626,7 @@
     <col width="46.5703125" customWidth="1" style="23" min="1" max="1"/>
     <col width="54.140625" customWidth="1" style="23" min="2" max="2"/>
     <col width="12" customWidth="1" style="23" min="3" max="3"/>
-    <col width="14.28515625" bestFit="1" customWidth="1" style="94" min="4" max="4"/>
+    <col width="14.28515625" bestFit="1" customWidth="1" style="95" min="4" max="4"/>
     <col width="21" bestFit="1" customWidth="1" style="28" min="5" max="5"/>
     <col width="46.85546875" customWidth="1" style="29" min="6" max="6"/>
     <col width="9.140625" bestFit="1" customWidth="1" style="28" min="7" max="7"/>
@@ -2656,7 +2706,7 @@
         </is>
       </c>
       <c r="C2" s="14" t="n"/>
-      <c r="D2" s="95" t="inlineStr">
+      <c r="D2" s="96" t="inlineStr">
         <is>
           <t>124, 570.12</t>
         </is>
@@ -2713,7 +2763,7 @@
         </is>
       </c>
       <c r="C3" s="14" t="n"/>
-      <c r="D3" s="95" t="n">
+      <c r="D3" s="96" t="n">
         <v>518743.75</v>
       </c>
       <c r="E3" s="22" t="inlineStr">
@@ -2758,7 +2808,7 @@
         </is>
       </c>
       <c r="C4" s="14" t="n"/>
-      <c r="D4" s="95" t="n">
+      <c r="D4" s="96" t="n">
         <v>246584.79</v>
       </c>
       <c r="E4" s="22" t="inlineStr">
@@ -2891,7 +2941,7 @@
         </is>
       </c>
       <c r="C7" s="7" t="n"/>
-      <c r="D7" s="95" t="n">
+      <c r="D7" s="96" t="n">
         <v>118418</v>
       </c>
       <c r="E7" s="22" t="inlineStr">
@@ -2977,7 +3027,7 @@
         </is>
       </c>
       <c r="C9" s="14" t="n"/>
-      <c r="D9" s="96" t="n">
+      <c r="D9" s="97" t="n">
         <v>6268828.8</v>
       </c>
       <c r="E9" s="24" t="inlineStr">
@@ -3039,288 +3089,288 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="97" t="inlineStr">
+      <c r="A1" s="98" t="inlineStr">
         <is>
           <t>Beneficiary Category</t>
         </is>
       </c>
-      <c r="B1" s="97" t="inlineStr">
+      <c r="B1" s="98" t="inlineStr">
         <is>
           <t>Indicator</t>
         </is>
       </c>
     </row>
     <row r="2" ht="30" customHeight="1">
-      <c r="A2" s="98" t="inlineStr">
+      <c r="A2" s="99" t="inlineStr">
         <is>
           <t>Electricity Access</t>
         </is>
       </c>
-      <c r="B2" s="98" t="inlineStr">
+      <c r="B2" s="99" t="inlineStr">
         <is>
           <t>Number of people, disaggregated by sex, who gain access to clean electricity (direct access to electricity, lighting, cooling, etc.).</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="98" t="inlineStr">
+      <c r="A3" s="99" t="inlineStr">
         <is>
           <t>Energy (MW added)</t>
         </is>
       </c>
-      <c r="B3" s="98" t="inlineStr">
+      <c r="B3" s="99" t="inlineStr">
         <is>
           <t>Installed renewable or clean-energy power capacity added, in MW.</t>
         </is>
       </c>
     </row>
     <row r="4" ht="30" customHeight="1">
-      <c r="A4" s="98" t="inlineStr">
+      <c r="A4" s="99" t="inlineStr">
         <is>
           <t>Energy Storage (MW)</t>
         </is>
       </c>
-      <c r="B4" s="98" t="inlineStr">
+      <c r="B4" s="99" t="inlineStr">
         <is>
           <t>Installed energy storage power capacity added, in MW.</t>
         </is>
       </c>
     </row>
     <row r="5" ht="30" customHeight="1">
-      <c r="A5" s="98" t="inlineStr">
+      <c r="A5" s="99" t="inlineStr">
         <is>
           <t>Clean Cooking</t>
         </is>
       </c>
-      <c r="B5" s="98" t="inlineStr">
+      <c r="B5" s="99" t="inlineStr">
         <is>
           <t>Number of people who gain access to clean cooking (direct access to clean cook stoves, clean fuels, biomass, etc.).</t>
         </is>
       </c>
     </row>
     <row r="6" ht="60" customHeight="1">
-      <c r="A6" s="98" t="inlineStr">
+      <c r="A6" s="99" t="inlineStr">
         <is>
           <t>Clean Heating</t>
         </is>
       </c>
-      <c r="B6" s="98" t="inlineStr">
+      <c r="B6" s="99" t="inlineStr">
         <is>
           <t>Number of people who gain access to clean heating (direct access to clean electric heaters, clean fuels, etc.).</t>
         </is>
       </c>
     </row>
     <row r="7" ht="30" customHeight="1">
-      <c r="A7" s="98" t="inlineStr">
+      <c r="A7" s="99" t="inlineStr">
         <is>
           <t>Agriculture and Food System</t>
         </is>
       </c>
-      <c r="B7" s="98" t="inlineStr">
+      <c r="B7" s="99" t="inlineStr">
         <is>
           <t>Number of people who gain access to clean, affordable, and sustainable energy for agricultural and food-system activities.</t>
         </is>
       </c>
     </row>
     <row r="8" ht="30" customHeight="1">
-      <c r="A8" s="98" t="inlineStr">
+      <c r="A8" s="99" t="inlineStr">
         <is>
           <t>Health Services</t>
         </is>
       </c>
-      <c r="B8" s="98" t="inlineStr">
+      <c r="B8" s="99" t="inlineStr">
         <is>
           <t>Number of people who gain access to health care facilities through clean energy systems.</t>
         </is>
       </c>
     </row>
     <row r="9" ht="30" customHeight="1">
-      <c r="A9" s="98" t="inlineStr">
+      <c r="A9" s="99" t="inlineStr">
         <is>
           <t>Water Services</t>
         </is>
       </c>
-      <c r="B9" s="98" t="inlineStr">
+      <c r="B9" s="99" t="inlineStr">
         <is>
           <t>Number of people who gain access to water services through clean energy systems.</t>
         </is>
       </c>
     </row>
     <row r="10" ht="30" customHeight="1">
-      <c r="A10" s="98" t="inlineStr">
+      <c r="A10" s="99" t="inlineStr">
         <is>
           <t>Education Services</t>
         </is>
       </c>
-      <c r="B10" s="98" t="inlineStr">
+      <c r="B10" s="99" t="inlineStr">
         <is>
           <t>Number of people who gain access to education services through clean energy systems, including students and teachers.</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="98" t="inlineStr">
+      <c r="A11" s="99" t="inlineStr">
         <is>
           <t>Transportation and E-mobility Services</t>
         </is>
       </c>
-      <c r="B11" s="98" t="inlineStr">
+      <c r="B11" s="99" t="inlineStr">
         <is>
           <t>Number of people served or energy saved from transport and e-mobility interventions, such as electric vehicles or charging stations.</t>
         </is>
       </c>
     </row>
     <row r="12" ht="30" customHeight="1">
-      <c r="A12" s="98" t="inlineStr">
+      <c r="A12" s="99" t="inlineStr">
         <is>
           <t>Energy Efficiency Services</t>
         </is>
       </c>
-      <c r="B12" s="98" t="inlineStr">
+      <c r="B12" s="99" t="inlineStr">
         <is>
           <t>Energy saved from energy-efficiency interventions, such as building or industrial efficiency.</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="98" t="inlineStr">
+      <c r="A13" s="99" t="inlineStr">
         <is>
           <t>Energy Infrastructure Services</t>
         </is>
       </c>
-      <c r="B13" s="98" t="inlineStr">
+      <c r="B13" s="99" t="inlineStr">
         <is>
           <t>Number of people benefiting from energy infrastructure interventions, such as streetlights, transmission, and distribution lines.</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="98" t="inlineStr">
+      <c r="A14" s="99" t="inlineStr">
         <is>
           <t>Other Energy Services</t>
         </is>
       </c>
-      <c r="B14" s="98" t="inlineStr">
+      <c r="B14" s="99" t="inlineStr">
         <is>
           <t>Access to other energy services not captured by the categories above.</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="98" t="inlineStr">
+      <c r="A15" s="99" t="inlineStr">
         <is>
           <t>Financing support</t>
         </is>
       </c>
-      <c r="B15" s="98" t="inlineStr">
+      <c r="B15" s="99" t="inlineStr">
         <is>
           <t>Support for the development of the energy market ecosystem.</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="98" t="inlineStr">
+      <c r="A16" s="99" t="inlineStr">
         <is>
           <t>Medium Enterprises</t>
         </is>
       </c>
-      <c r="B16" s="98" t="inlineStr">
+      <c r="B16" s="99" t="inlineStr">
         <is>
           <t>Support for the development of medium enterprises in the energy transition market.</t>
         </is>
       </c>
     </row>
     <row r="17" ht="30" customHeight="1">
-      <c r="A17" s="98" t="inlineStr">
+      <c r="A17" s="99" t="inlineStr">
         <is>
           <t>Small Enterprises</t>
         </is>
       </c>
-      <c r="B17" s="98" t="inlineStr">
+      <c r="B17" s="99" t="inlineStr">
         <is>
           <t>Support for the development of small enterprises in the energy transition market.</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="98" t="inlineStr">
+      <c r="A18" s="99" t="inlineStr">
         <is>
           <t>Capacity Building Training</t>
         </is>
       </c>
-      <c r="B18" s="98" t="inlineStr">
+      <c r="B18" s="99" t="inlineStr">
         <is>
           <t>Number of people benefiting from training on energy business, energy finance, or related implementation capacity.</t>
         </is>
       </c>
     </row>
     <row r="19" ht="45" customHeight="1">
-      <c r="A19" s="98" t="inlineStr">
+      <c r="A19" s="99" t="inlineStr">
         <is>
           <t>Entrepreneurship Training</t>
         </is>
       </c>
-      <c r="B19" s="98" t="inlineStr">
+      <c r="B19" s="99" t="inlineStr">
         <is>
           <t>Training for enterprises on the energy business, assumed to result in direct beneficiaries.</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="98" t="inlineStr">
+      <c r="A20" s="99" t="inlineStr">
         <is>
           <t>Market Intervention</t>
         </is>
       </c>
-      <c r="B20" s="98" t="inlineStr">
+      <c r="B20" s="99" t="inlineStr">
         <is>
           <t>Volume of investment leveraged or barriers removed for clean, reliable, affordable, and sustainable energy solutions.</t>
         </is>
       </c>
     </row>
     <row r="21" ht="30" customHeight="1">
-      <c r="A21" s="98" t="inlineStr">
+      <c r="A21" s="99" t="inlineStr">
         <is>
           <t>Campaign Participant</t>
         </is>
       </c>
-      <c r="B21" s="98" t="inlineStr">
+      <c r="B21" s="99" t="inlineStr">
         <is>
           <t>Individuals who participate in advocacy or awareness campaigns on energy.</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="98" t="inlineStr">
+      <c r="A22" s="99" t="inlineStr">
         <is>
           <t>Policy or Regulatory Framework</t>
         </is>
       </c>
-      <c r="B22" s="98" t="inlineStr">
+      <c r="B22" s="99" t="inlineStr">
         <is>
           <t>Policies, regulations, strategies, plans, or frameworks developed, approved, implemented, or strengthened.</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="98" t="inlineStr">
+      <c r="A23" s="99" t="inlineStr">
         <is>
           <t>GHG Emissions Reduction</t>
         </is>
       </c>
-      <c r="B23" s="98" t="inlineStr">
+      <c r="B23" s="99" t="inlineStr">
         <is>
           <t>Greenhouse gas emissions reduced or mitigated, in tCO2e.</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="98" t="inlineStr">
+      <c r="A24" s="99" t="inlineStr">
         <is>
           <t>Other</t>
         </is>
       </c>
-      <c r="B24" s="98" t="inlineStr">
+      <c r="B24" s="99" t="inlineStr">
         <is>
           <t>Energy-related output that does not fit the standard categories above.</t>
         </is>
